--- a/stochastic_data.xlsx
+++ b/stochastic_data.xlsx
@@ -1,50 +1,165 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ecc8d9ed5a21f5e/Έγγραφα/python/MS-Thesis-Codes/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_AA4594BF45D313F5986B34BE6E07397CB5313E4D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F3C3F0E-A003-4408-A2A2-9EA6F614EAF8}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
+    <sheet name="Factories" sheetId="2" r:id="rId2"/>
+    <sheet name="Orders" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+  <si>
+    <t>order_id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>duration (h)</t>
+  </si>
+  <si>
+    <t>consumption (MW/h)</t>
+  </si>
+  <si>
+    <t>revenue (€)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>scenario_id</t>
+  </si>
+  <si>
+    <t>probability</t>
+  </si>
+  <si>
+    <t>hour_0</t>
+  </si>
+  <si>
+    <t>hour_1</t>
+  </si>
+  <si>
+    <t>hour_2</t>
+  </si>
+  <si>
+    <t>hour_3</t>
+  </si>
+  <si>
+    <t>hour_4</t>
+  </si>
+  <si>
+    <t>hour_5</t>
+  </si>
+  <si>
+    <t>hour_6</t>
+  </si>
+  <si>
+    <t>hour_7</t>
+  </si>
+  <si>
+    <t>hour_8</t>
+  </si>
+  <si>
+    <t>hour_9</t>
+  </si>
+  <si>
+    <t>hour_10</t>
+  </si>
+  <si>
+    <t>hour_11</t>
+  </si>
+  <si>
+    <t>hour_12</t>
+  </si>
+  <si>
+    <t>hour_13</t>
+  </si>
+  <si>
+    <t>hour_14</t>
+  </si>
+  <si>
+    <t>hour_15</t>
+  </si>
+  <si>
+    <t>hour_16</t>
+  </si>
+  <si>
+    <t>hour_17</t>
+  </si>
+  <si>
+    <t>hour_18</t>
+  </si>
+  <si>
+    <t>hour_19</t>
+  </si>
+  <si>
+    <t>hour_20</t>
+  </si>
+  <si>
+    <t>hour_21</t>
+  </si>
+  <si>
+    <t>hour_22</t>
+  </si>
+  <si>
+    <t>hour_23</t>
+  </si>
+  <si>
+    <t>factory_id</t>
+  </si>
+  <si>
+    <t>compatible_order_types</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="161"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -60,7 +175,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,107 +198,43 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -482,383 +533,327 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>scenario_id</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>probability</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>hour_0</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>hour_1</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>hour_2</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>hour_3</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>hour_4</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>hour_5</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>hour_6</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>hour_7</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>hour_8</t>
-        </is>
-      </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
-          <t>hour_9</t>
-        </is>
-      </c>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>hour_10</t>
-        </is>
-      </c>
-      <c r="N1" s="5" t="inlineStr">
-        <is>
-          <t>hour_11</t>
-        </is>
-      </c>
-      <c r="O1" s="5" t="inlineStr">
-        <is>
-          <t>hour_12</t>
-        </is>
-      </c>
-      <c r="P1" s="5" t="inlineStr">
-        <is>
-          <t>hour_13</t>
-        </is>
-      </c>
-      <c r="Q1" s="5" t="inlineStr">
-        <is>
-          <t>hour_14</t>
-        </is>
-      </c>
-      <c r="R1" s="5" t="inlineStr">
-        <is>
-          <t>hour_15</t>
-        </is>
-      </c>
-      <c r="S1" s="5" t="inlineStr">
-        <is>
-          <t>hour_16</t>
-        </is>
-      </c>
-      <c r="T1" s="5" t="inlineStr">
-        <is>
-          <t>hour_17</t>
-        </is>
-      </c>
-      <c r="U1" s="5" t="inlineStr">
-        <is>
-          <t>hour_18</t>
-        </is>
-      </c>
-      <c r="V1" s="5" t="inlineStr">
-        <is>
-          <t>hour_19</t>
-        </is>
-      </c>
-      <c r="W1" s="5" t="inlineStr">
-        <is>
-          <t>hour_20</t>
-        </is>
-      </c>
-      <c r="X1" s="5" t="inlineStr">
-        <is>
-          <t>hour_21</t>
-        </is>
-      </c>
-      <c r="Y1" s="5" t="inlineStr">
-        <is>
-          <t>hour_22</t>
-        </is>
-      </c>
-      <c r="Z1" s="5" t="inlineStr">
-        <is>
-          <t>hour_23</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2">
+        <v>0.81850000000000001</v>
+      </c>
+      <c r="C2">
         <v>65.8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>63.32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>60.77</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>57.96</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>56.2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>57.35</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>61.39</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>67.19</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>70.16</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>66.64</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>60.82</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>56.6</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>54.43</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>53.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>52.25</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>54.97</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2">
         <v>60.73</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2">
         <v>67.81</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>75.09</v>
       </c>
-      <c r="V2" t="n">
-        <v>80.93000000000001</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="V2">
+        <v>80.930000000000007</v>
+      </c>
+      <c r="W2">
         <v>85.72</v>
       </c>
-      <c r="X2" t="n">
-        <v>83.95999999999999</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="X2">
+        <v>83.96</v>
+      </c>
+      <c r="Y2">
         <v>75.19</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2">
         <v>70.37</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>0.1489</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>177.42</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>168.03</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>164.33</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>153.6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>147.75</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>152.65</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>169.93</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>198.6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>217.87</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>207.33</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>186.66</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>171.96</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>165.72</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>163.25</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>158.34</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>169.25</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3">
         <v>189.19</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3">
         <v>216.79</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3">
         <v>239.32</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3">
         <v>260.11</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3">
         <v>278.82</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3">
         <v>254.03</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3">
         <v>215.38</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3">
         <v>195.65</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="C4">
         <v>373.82</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>356.6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>328.3</v>
       </c>
-      <c r="F4" t="n">
-        <v>304.03</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>304.02999999999997</v>
+      </c>
+      <c r="G4">
         <v>294.48</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>301</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>338.06</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>381.37</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>418.33</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>412.2</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>373.33</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>346.02</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>332.11</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>340.14</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>332.54</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4">
         <v>342.62</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4">
         <v>377.45</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4">
         <v>421.31</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4">
         <v>463.09</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4">
         <v>493.8</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W4">
         <v>521.14</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4">
         <v>491.53</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4">
         <v>436.09</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z4">
         <v>414.01</v>
       </c>
     </row>
@@ -868,74 +863,52 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="22" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="22" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>factory_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>compatible_order_types</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -944,134 +917,144 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="20" defaultRowHeight="14.4" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>profit (€)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>duration (h)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>consumption (MW/h)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14.4" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" s="2">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="14.4" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>32</v>
+      </c>
+      <c r="E3" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>300</v>
+      </c>
+      <c r="E4" s="2">
+        <v>120200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" ht="14.4" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" s="3">
+        <v>64</v>
+      </c>
+      <c r="E5" s="3">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="14.4" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" ht="14.4" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>32</v>
+      </c>
+      <c r="E7" s="3">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>
